--- a/outputs/evaluation/decision/v1/CF_M08/run_1/CF_M08_decision_eval.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M08/run_1/CF_M08_decision_eval.xlsx
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.375</v>
+        <v>0.2222</v>
       </c>
       <c r="C2" t="n">
-        <v>0.25</v>
+        <v>0.1667</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.8203</v>
       </c>
     </row>
     <row r="5">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.3889</v>
+        <v>0.75</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.375</v>
+        <v>0.2222</v>
       </c>
     </row>
     <row r="8">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.25</v>
+        <v>0.1667</v>
       </c>
     </row>
     <row r="9">
@@ -726,19 +726,19 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -755,28 +755,28 @@
         <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
         <v>3</v>
       </c>
-      <c r="H3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4</v>
-      </c>
       <c r="J3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -792,31 +792,31 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" t="n">
-        <v>8</v>
-      </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -829,22 +829,22 @@
         <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:U3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -974,7 +974,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7695</v>
+        <v>0.7936</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -992,7 +992,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1009,32 +1009,32 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3333</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Prisma is an ORM (Object-Relational Mapping) tool for databases. It is designed to simplify database access and management in Node.js and TypeScript applications.</t>
+          <t>Prisma is an ORM tool used to simplify database access and management.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>R_24, C_05</t>
+          <t>R_24, R_25, C_05</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>AU_04, AU_07, AU_08</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>42</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -1059,16 +1059,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M08_AD08</t>
+          <t>CF_M08_AD01</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.832</v>
+        <v>0.847</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1094,136 +1094,50 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3333</v>
+        <v>0.5</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Next.js is a framework for building web applications that supports both client-side and server-side rendering. [...] React is an open-source JavaScript library designed to build user interfaces.</t>
+          <t>Traefik acts as a reverse proxy and load balancer, improving the availability and responsiveness of the application.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>R_18, C_02</t>
+          <t>R_22, R_23, C_04</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>AU_03, AU_06, AU_15</t>
+          <t>AU_02, AU_05</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>42, 44, 47</t>
+          <t>43</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>React is an open source JavaScript library designed to build user interfaces (UI) efficiently and flexibly</t>
+          <t>Load Balancer: Distributes traffic between multiple instances of a service, improving the availability and responsiveness of the application</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>*CF_M08_C18, *CF_M08_C19</t>
+          <t>CF_M08_C08, *CF_M08_C09</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>CF_M08_AU06</t>
+          <t>CF_M08_AU03</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AD_02</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>CF_M08_AD02</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.9373</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Traefik opens port 80 to handle insecure HTTP traffic by redirecting this traffic to port 443 (HTTPS) to ensure that all communications are performed securely. [...] HTTPS encrypts the data transmitted between clients and the server, protecting the integrity and confidentiality of the information.</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>R_20, R_21, C_03</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>AU_02, AU_05</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>Traefik opens port 80 to handle non-secure HTTP traffic re-
-directing this traffic to port 443 (HTTPS) to ensure that all communications are carried out safely.</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>*CF_M08_C10</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>CF_M08_AU03</t>
-        </is>
-      </c>
-      <c r="U4" t="n">
         <v>43</v>
       </c>
     </row>
@@ -1238,7 +1152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1286,17 +1200,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The architecture implemented for the development of the Revivack project system is a microservices-based architecture. [...] In the case of this application, such services are executed in Amazon EC2 instances and are managed by Docker, which manages the execution of the containers.</t>
+          <t>The architecture implemented for the development of the Revivack project system is a microservices-based architecture.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>R_28, R_29</t>
+          <t>R_28, R_29, C_07</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P_01, AU_09</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1306,151 +1220,221 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M08_AD07</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6422</v>
+        <v>0.6187</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. [...] This approach promotes modularity, code reuse, and maintainability, facilitating the management of the application.</t>
+          <t>Next.js is a framework for building web applications that offers an additional structure, features and optimizations that allow building applications faster and without the need to configure tools manually.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>R_24, C_05</t>
+          <t>R_18, C_02</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_03, AU_06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M08_AD09</t>
+          <t>CF_M08_AD05</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.7319</v>
+        <v>0.7456</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance. It is generally used to manage shared resources, such as configurations, logs, or database connections, where having multiple instances could lead to inconsistent states or inefficient use of resources.</t>
+          <t>PostgreSQL provides the relational database for storing application data.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C_04</t>
+          <t>R_07, R_30, R_31, C_03</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>AU_04, AU_07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M08_AD10</t>
+          <t>CF_M08_AD11</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.639</v>
+        <v>0.7294</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AD_07</t>
+          <t>AD_06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>It is used to interact with the S3 (Simple Storage Service) service of AWS (Amazon Web Services). It has been used to manage cloud storage, allowing uploading, downloading, and managing files in S3 'buckets'.</t>
+          <t>Docker is a containerization platform used to manage the execution of the application services.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>R_07</t>
+          <t>C_06</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M08_AD10</t>
+          <t>CF_M08_AD01</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.656</v>
+        <v>0.6374</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>AD_07</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components, which promotes modularity, code reuse, and maintainability.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>R_18, C_02</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>P_02</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CF_M08_AD09</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7342</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>AD_08</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Stripe is used to handle online payments. It has been used to easily integrate payment processing functionalities into the application.</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>R_14, R_15</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>AU_11</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>CF_M08_AD07</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>0.6778</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>The Observer pattern establishes a one-to-many relationship between objects, where a subject maintains a list of observers, allowing them to react appropriately when the subject's state changes.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>C_05</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>P_03</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CF_M08_AD01</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6075</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AD_09</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance, used to manage shared resources where having multiple instances could lead to inconsistent states or inefficient resource use.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>C_05</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>P_04</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CF_M08_AD01</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.6326000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1464,7 +1448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1507,17 +1491,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M08_AD02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Load Balancer: Distributes traffic between multiple instances of a service, improving the availability and responsiveness of the application</t>
+          <t>Traefik opens port 80 to handle non-secure HTTP traffic re-
+directing this traffic to port 443 (HTTPS) to ensure that all communications are carried out safely.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CF_M08_C08, *CF_M08_C09</t>
+          <t>*CF_M08_C10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1530,11 +1515,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6422</v>
+        <v>0.7261</v>
       </c>
     </row>
     <row r="3">
@@ -1567,7 +1552,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.8751</v>
+        <v>0.5949</v>
       </c>
     </row>
     <row r="4">
@@ -1596,11 +1581,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.5889</v>
+        <v>0.6263</v>
       </c>
     </row>
     <row r="5">
@@ -1633,7 +1618,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.7422</v>
+        <v>0.7456</v>
       </c>
     </row>
     <row r="6">
@@ -1662,11 +1647,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.6411</v>
+        <v>0.7246</v>
       </c>
     </row>
     <row r="7">
@@ -1695,27 +1680,27 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_07</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.7027</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M08_AD09</t>
+          <t>CF_M08_AD08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>React allows developers to create dynamic and fast web applications by facilitating the creation of reusable and modular components</t>
+          <t>React is an open source JavaScript library designed to build user interfaces (UI) efficiently and flexibly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>*CF_M08_C20, *CF_M08_C21</t>
+          <t>*CF_M08_C18, *CF_M08_C19</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1728,60 +1713,60 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_07</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.7641</v>
+        <v>0.6975</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M08_AD10</t>
+          <t>CF_M08_AD09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>It is designed to simplify access and database management</t>
+          <t>React allows developers to create dynamic and fast web applications by facilitating the creation of reusable and modular components</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>*CF_M08_C22</t>
+          <t>*CF_M08_C20, *CF_M08_C21</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CF_M08_AU09</t>
+          <t>CF_M08_AU06</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_07</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.7452</v>
+        <v>0.7342</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M08_AD11</t>
+          <t>CF_M08_AD10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Prisma is compatible with several databases, including PostgreSQL, MySQL, SQLite and SQL Server.</t>
+          <t>It is designed to simplify access and database management</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>*CF_M08_C23</t>
+          <t>*CF_M08_C22</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1794,11 +1779,44 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.7682</v>
+        <v>0.7812</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CF_M08_AD11</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Prisma is compatible with several databases, including PostgreSQL, MySQL, SQLite and SQL Server.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>*CF_M08_C23</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CF_M08_AU09</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>50</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0.7723</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/decision/v1/CF_M08/run_1/CF_M08_decision_eval.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M08/run_1/CF_M08_decision_eval.xlsx
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2222</v>
+        <v>0.5</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1667</v>
+        <v>0.1429</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8203</v>
+        <v>0.8122</v>
       </c>
     </row>
     <row r="5">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.75</v>
+        <v>0.1667</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2222</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1667</v>
+        <v>0.1429</v>
       </c>
     </row>
     <row r="9">
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
@@ -752,10 +752,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -776,7 +776,7 @@
         <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -789,10 +789,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
@@ -801,7 +801,7 @@
         <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
@@ -813,10 +813,10 @@
         <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
@@ -838,7 +838,7 @@
         <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
@@ -974,16 +974,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M08_AD12</t>
+          <t>CF_M08_AD11</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7936</v>
+        <v>0.7667</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -992,7 +992,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1009,42 +1009,42 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0.3333</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Prisma is an ORM tool used to simplify database access and management.</t>
+          <t>System Service (Next.js) [...] Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM [...] Prisma Client es una biblioteca de consultas generada automáticamente para realizar operaciones con bases de datos. Proporciona una API para crear, leer, actualizar y eliminar datos en la base de datos.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>R_24, R_25, C_05</t>
+          <t>C_05</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_04, AU_07, AU_08</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>42, 50</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Prisma Studio is a visual tool to explore and edit data in the database. It provides a graphical interface to visualize and manipulate the data, facilitating development and debugging.</t>
+          <t>Prisma is compatible with several databases, including PostgreSQL, MySQL, SQLite and SQL Server.</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>*CF_M08_C24</t>
+          <t>*CF_M08_C23</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1059,16 +1059,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M08_AD03</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.847</v>
+        <v>0.8576</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1088,33 +1088,35 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Traefik acts as a reverse proxy and load balancer, improving the availability and responsiveness of the application.</t>
+          <t>Puerto443(HTTPS) :Traefikabreelpuerto443paramanejartráficoHTTPS,queesel estándar para comunicaciones seguras en la web. HTTPS cifra los datos transmitidos entre los clientes y el servidor, protegiendo la integridad y confidencialidad de la información.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>R_22, R_23, C_04</t>
+          <t>R_20, R_21, C_03</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>AU_02, AU_05</t>
+          <t>AU_02, AU_05, AU_23, AU_24</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -1124,17 +1126,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Load Balancer: Distributes traffic between multiple instances of a service, improving the availability and responsiveness of the application</t>
+          <t>HTTPS encrypts the data transmitted between the clients and the server, protecting the integrity and confidentiality of the information.</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>CF_M08_C08, *CF_M08_C09</t>
+          <t>*CF_M08_C11, *CF_M08_C12</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>CF_M08_AU03</t>
+          <t>CF_M08_AU22</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -1152,7 +1154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1195,27 +1197,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The architecture implemented for the development of the Revivack project system is a microservices-based architecture.</t>
+          <t>Next.js soporta tanto el renderizado de componentes en el lado del cliente (CSR) como el renderizado en el lado del servidor (SSR), utilizando las server actions [...] para comunicar los componentes de cliente con el servidor.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>R_28, R_29, C_07</t>
+          <t>R_18, C_02</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_03, AU_06, AU_15</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1224,217 +1226,42 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6187</v>
+        <v>0.7244</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Next.js is a framework for building web applications that offers an additional structure, features and optimizations that allow building applications faster and without the need to configure tools manually.</t>
+          <t>La arquitectura implementada para el desarrollo del sistema del proyecto Revivack es una arquitectura basada en microservicios. La arquitectura de software basada en microservicios es un enfoque de diseño y desarrollo de software donde una aplicación se construye como una colección de servicios pequeños e independientes que se comunican entre sí. En el caso de esta aplicación, dichos servicios se ejecutan en instancias de Amazon EC2 y son gestionados por Docker, que administra la ejecución de los contenedores.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>R_18, C_02</t>
+          <t>R_22, R_28, C_04, C_07</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AU_03, AU_06</t>
+          <t>AU_09, P_01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M08_AD05</t>
+          <t>CF_M08_AD14</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.7456</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AD_04</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>PostgreSQL provides the relational database for storing application data.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>R_07, R_30, R_31, C_03</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>AU_04, AU_07</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>CF_M08_AD11</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>0.7294</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AD_06</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Docker is a containerization platform used to manage the execution of the application services.</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>C_06</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>AU_09</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>CF_M08_AD01</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>0.6374</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AD_07</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components, which promotes modularity, code reuse, and maintainability.</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>R_18, C_02</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>P_02</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>CF_M08_AD09</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>0.7342</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AD_08</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>The Observer pattern establishes a one-to-many relationship between objects, where a subject maintains a list of observers, allowing them to react appropriately when the subject's state changes.</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>C_05</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>CF_M08_AD01</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>0.6075</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>AD_09</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance, used to manage shared resources where having multiple instances could lead to inconsistent states or inefficient resource use.</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>C_05</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>CF_M08_AD01</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>0.6326000000000001</v>
+        <v>0.6768</v>
       </c>
     </row>
   </sheetData>
@@ -1448,7 +1275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1491,56 +1318,56 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>CF_M08_AD01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Load Balancer: Distributes traffic between multiple instances of a service, improving the availability and responsiveness of the application</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CF_M08_C08, *CF_M08_C09</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CF_M08_AU03</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>43</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6381</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>CF_M08_AD02</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Traefik opens port 80 to handle non-secure HTTP traffic re-
 directing this traffic to port 443 (HTTPS) to ensure that all communications are carried out safely.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>*CF_M08_C10</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>CF_M08_AU03</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>43</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>AD_02</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>0.7261</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CF_M08_AD03</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>HTTPS encrypts the data transmitted between the clients and the server, protecting the integrity and confidentiality of the information.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>*CF_M08_C11, *CF_M08_C12</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CF_M08_AU22</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1548,11 +1375,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.5949</v>
+        <v>0.8139999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1581,11 +1408,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.6263</v>
+        <v>0.534</v>
       </c>
     </row>
     <row r="5">
@@ -1614,11 +1441,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.7456</v>
+        <v>0.7020999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1647,11 +1474,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.7246</v>
+        <v>0.6147</v>
       </c>
     </row>
     <row r="7">
@@ -1680,11 +1507,11 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AD_07</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.677</v>
+        <v>0.7244</v>
       </c>
     </row>
     <row r="8">
@@ -1713,11 +1540,11 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AD_07</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.6975</v>
+        <v>0.6254</v>
       </c>
     </row>
     <row r="9">
@@ -1746,11 +1573,11 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AD_07</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.7342</v>
+        <v>0.6435999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1779,27 +1606,27 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.7812</v>
+        <v>0.6754</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF_M08_AD11</t>
+          <t>CF_M08_AD12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Prisma is compatible with several databases, including PostgreSQL, MySQL, SQLite and SQL Server.</t>
+          <t>Prisma Studio is a visual tool to explore and edit data in the database. It provides a graphical interface to visualize and manipulate the data, facilitating development and debugging.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>*CF_M08_C23</t>
+          <t>*CF_M08_C24</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1812,11 +1639,77 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.7723</v>
+        <v>0.7242</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CF_M08_AD13</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>It is generally used for manage shared resources, such as configurations, records or connections to databases data, where having multiple instances could lead to inconsistent states or usage resource inefficient.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CF_M08_C06</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CF_M08_P05</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>67</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CF_M08_AD14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>This approach promotes modularity, code reuse and maintainability, facilitating the management of the application</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>*CF_M08_C21, CF_M08_C05</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CF_M08_P03</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>66</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0.6768</v>
       </c>
     </row>
   </sheetData>
